--- a/public/trip-template.xlsx
+++ b/public/trip-template.xlsx
@@ -4,8 +4,9 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Trip" sheetId="1" r:id="rId1"/>
-    <sheet name="Schedule" sheetId="2" r:id="rId2"/>
-    <sheet name="Legend" sheetId="3" r:id="rId3"/>
+    <sheet name="Steps" sheetId="2" r:id="rId2"/>
+    <sheet name="Hotels" sheetId="3" r:id="rId3"/>
+    <sheet name="Cash" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -462,303 +463,434 @@
         <v>notes</v>
       </c>
       <c r="B8" t="str">
-        <v>Fill Schedule rows. Download from the app after edits for round-trip.</v>
+        <v>Fill Steps + Hotels. Cash is filled automatically on export.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>How to use</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Edit the Steps sheet for day plans (sights, food, drives, flights). Use Hotels for stays. Cash is a read-only spend snapshot.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Row 2 under each table shows Required/Optional and the preferred format. Import also accepts other common date/time styles.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Preferred date: YYYY-MM-DD · Preferred time: HH:MM (24h).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:T4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>id</v>
+        <v>Date</v>
       </c>
       <c r="B1" t="str">
-        <v>date</v>
+        <v>Start</v>
       </c>
       <c r="C1" t="str">
-        <v>end_date</v>
+        <v>End</v>
       </c>
       <c r="D1" t="str">
-        <v>start</v>
+        <v>Type</v>
       </c>
       <c r="E1" t="str">
-        <v>end</v>
+        <v>Title</v>
       </c>
       <c r="F1" t="str">
-        <v>type</v>
+        <v>Place</v>
       </c>
       <c r="G1" t="str">
-        <v>title</v>
+        <v>City</v>
       </c>
       <c r="H1" t="str">
-        <v>place</v>
+        <v>From</v>
       </c>
       <c r="I1" t="str">
-        <v>city</v>
+        <v>To</v>
       </c>
       <c r="J1" t="str">
-        <v>from</v>
+        <v>Confirm</v>
       </c>
       <c r="K1" t="str">
-        <v>to</v>
+        <v>Cost</v>
       </c>
       <c r="L1" t="str">
-        <v>confirm</v>
+        <v>Currency</v>
       </c>
       <c r="M1" t="str">
-        <v>cost</v>
+        <v>Status</v>
       </c>
       <c r="N1" t="str">
-        <v>currency</v>
+        <v>Notes</v>
       </c>
       <c r="O1" t="str">
-        <v>status</v>
+        <v>URL</v>
       </c>
       <c r="P1" t="str">
-        <v>notes</v>
+        <v>Tags</v>
       </c>
       <c r="Q1" t="str">
-        <v>url</v>
+        <v>Lat</v>
       </c>
       <c r="R1" t="str">
-        <v>tags</v>
+        <v>Lon</v>
       </c>
       <c r="S1" t="str">
-        <v>lat</v>
+        <v>Lat to</v>
       </c>
       <c r="T1" t="str">
-        <v>lon</v>
-      </c>
-      <c r="U1" t="str">
-        <v>lat_to</v>
-      </c>
-      <c r="V1" t="str">
-        <v>lon_to</v>
-      </c>
-      <c r="W1" t="str">
-        <v>wikidata</v>
-      </c>
-      <c r="X1" t="str">
-        <v>osm_id</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>geocode_query</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>updated_at</v>
+        <v>Lon to</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>F01</v>
+        <v>Required · YYYY-MM-DD</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-10-01</v>
+        <v>Optional · HH:MM (24h)</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Optional · HH:MM (24h)</v>
       </c>
       <c r="D2" t="str">
-        <v>10:00</v>
+        <v>Required · flight, train, bus, ferry, drive, sight, restaurant, activity, city, note, other</v>
       </c>
       <c r="E2" t="str">
-        <v>13:00</v>
+        <v>Required · free text</v>
       </c>
       <c r="F2" t="str">
-        <v>flight</v>
+        <v>Optional · free text</v>
       </c>
       <c r="G2" t="str">
-        <v>Example flight</v>
+        <v>Optional · free text</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Optional · place or IATA</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>Optional · place or IATA</v>
       </c>
       <c r="J2" t="str">
-        <v>TLV</v>
+        <v>Optional · booking ref</v>
       </c>
       <c r="K2" t="str">
-        <v>CDG</v>
+        <v>Optional · number ≥ 0</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>Optional · 3-letter code (EUR)</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Optional · planned / booked / done / cancelled</v>
       </c>
       <c r="N2" t="str">
-        <v>EUR</v>
+        <v>Optional · free text</v>
       </c>
       <c r="O2" t="str">
-        <v>planned</v>
+        <v>Optional · https://…</v>
       </c>
       <c r="P2" t="str">
-        <v>Replace with your flight</v>
+        <v>Optional · comma-separated</v>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>Optional · decimal degrees</v>
       </c>
       <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
-      </c>
-      <c r="Z2" t="str">
-        <v>2026-09-10T17:55:43.503Z</v>
+        <v>Optional · decimal degrees</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Optional · decimal degrees</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Optional · decimal degrees</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>H01</v>
+        <v>2026-10-01</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-10-01</v>
+        <v>10:00</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-10-03</v>
+        <v>13:00</v>
       </c>
       <c r="D3" t="str">
-        <v>15:00</v>
+        <v>flight</v>
       </c>
       <c r="E3" t="str">
+        <v>Example flight</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>TLV</v>
+      </c>
+      <c r="I3" t="str">
+        <v>CDG</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="M3" t="str">
+        <v>planned</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Replace with your flight</v>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="B4" t="str">
         <v>11:00</v>
       </c>
-      <c r="F3" t="str">
-        <v>hotel</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Example hotel</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Hotel name</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>sight</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Example sight</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
         <v>Paris</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>EUR</v>
       </c>
-      <c r="O3" t="str">
+      <c r="M4" t="str">
         <v>planned</v>
       </c>
-      <c r="P3" t="str">
-        <v>2 nights example</v>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="W3" t="str">
-        <v/>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v/>
-      </c>
-      <c r="Z3" t="str">
-        <v>2026-09-10T17:55:43.503Z</v>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Check-in</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Check-out</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Hotel</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Place</v>
+      </c>
+      <c r="E1" t="str">
+        <v>City</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Confirm</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Cost</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Currency</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="K1" t="str">
+        <v>URL</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Lat</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Lon</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Required · YYYY-MM-DD</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Preferred · YYYY-MM-DD (defaults to check-in)</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Required · free text</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Optional · free text</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Optional · free text</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Optional · booking ref</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Optional · number ≥ 0</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Optional · 3-letter code (EUR)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Optional · planned / booked / done / cancelled</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Optional · free text</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Optional · https://…</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Optional · decimal degrees</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Optional · decimal degrees</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-10-03</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Example hotel</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Hotel name</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="I3" t="str">
+        <v>planned</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2 nights example</v>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Column / Value</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Meaning</v>
+        <v>Cash snapshot (export only — ignored when importing)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Schedule sheet</v>
-      </c>
-      <c r="B2" t="str">
-        <v>One row per event in chronological order — the sheet you keep up with</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>type values</v>
-      </c>
-      <c r="B3" t="str">
-        <v>flight, train, bus, ferry, drive, hotel, sight, restaurant, activity, city, note, other</v>
+        <v>Amounts as entered (no FX conversion)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>status values</v>
+        <v>By type</v>
       </c>
       <c r="B4" t="str">
-        <v>planned, booked, done, cancelled</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>from / to</v>
-      </c>
-      <c r="B5" t="str">
-        <v>For flights use IATA (TLV, CDG). For drives use place names</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>end_date</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Hotel checkout or overnight flight/train arrival date</v>
+        <v>(none)</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>lat / lon</v>
+        <v>By currency</v>
       </c>
       <c r="B7" t="str">
-        <v>Optional; app fills on enrich/export</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>All times</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Local wall clock — never UTC in this workbook</v>
+        <v>(none)</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
